--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:14</t>
+    <t xml:space="preserve">2026-09-09 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:09</t>
+    <t xml:space="preserve">2026-09-17 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:05</t>
+    <t xml:space="preserve">2026-09-23 12:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:34</t>
+    <t xml:space="preserve">2026-10-02 13:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:56</t>
+    <t xml:space="preserve">2026-10-05 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>305451.62</v>
+        <v>305451.63</v>
       </c>
     </row>
     <row r="3">
@@ -585,7 +585,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>279420.12</v>
+        <v>279420.13</v>
       </c>
     </row>
     <row r="4">
@@ -687,7 +687,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>221100.12</v>
+        <v>221100.13</v>
       </c>
     </row>
     <row r="10">
